--- a/research/traditional_assets/database/data/pakistan/pakistan_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0476</v>
+        <v>0.07164999999999999</v>
       </c>
       <c r="E2">
-        <v>0.0261</v>
+        <v>-0.04205</v>
       </c>
       <c r="G2">
-        <v>0.07412328917715605</v>
+        <v>0.05564660535979848</v>
       </c>
       <c r="H2">
-        <v>0.07412328917715605</v>
+        <v>0.05564660535979848</v>
       </c>
       <c r="I2">
-        <v>0.05032171679207117</v>
+        <v>0.05283185060454156</v>
       </c>
       <c r="J2">
-        <v>0.04260037036598883</v>
+        <v>0.04160696119089036</v>
       </c>
       <c r="K2">
-        <v>34.26</v>
+        <v>30.221</v>
       </c>
       <c r="L2">
-        <v>0.04707854669378332</v>
+        <v>0.04586026890042186</v>
       </c>
       <c r="M2">
-        <v>22.34</v>
+        <v>13.72</v>
       </c>
       <c r="N2">
-        <v>0.05672930421533773</v>
+        <v>0.05782929399367756</v>
       </c>
       <c r="O2">
-        <v>0.6520723876240514</v>
+        <v>0.4539889480824592</v>
       </c>
       <c r="P2">
-        <v>22.34</v>
+        <v>13.72</v>
       </c>
       <c r="Q2">
-        <v>0.05672930421533773</v>
+        <v>0.05782929399367756</v>
       </c>
       <c r="R2">
-        <v>0.6520723876240514</v>
+        <v>0.4539889480824592</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>278.041</v>
+        <v>156.742</v>
       </c>
       <c r="V2">
-        <v>0.7060462163534789</v>
+        <v>0.6606617492096943</v>
       </c>
       <c r="W2">
-        <v>0.05331462644686075</v>
+        <v>0.08802311842854724</v>
       </c>
       <c r="X2">
-        <v>0.121611232127691</v>
+        <v>0.1954706322120505</v>
       </c>
       <c r="Y2">
-        <v>-0.06829660568083021</v>
+        <v>-0.1074475137835033</v>
       </c>
       <c r="Z2">
-        <v>2.664163524656602</v>
+        <v>2.129098112211642</v>
       </c>
       <c r="AA2">
-        <v>-0.0912446896590767</v>
+        <v>0.5035872364730174</v>
       </c>
       <c r="AB2">
-        <v>0.1195838589605399</v>
+        <v>0.1912075399552062</v>
       </c>
       <c r="AC2">
-        <v>-0.2108285486196166</v>
+        <v>0.3115302561725815</v>
       </c>
       <c r="AD2">
-        <v>38.588</v>
+        <v>24.68</v>
       </c>
       <c r="AE2">
-        <v>0.1194012803698165</v>
+        <v>0.9143354430960023</v>
       </c>
       <c r="AF2">
-        <v>38.70740128036982</v>
+        <v>25.594335443096</v>
       </c>
       <c r="AG2">
-        <v>-239.3335987196302</v>
+        <v>-131.147664556904</v>
       </c>
       <c r="AH2">
-        <v>0.08949535005824795</v>
+        <v>0.09737449886431736</v>
       </c>
       <c r="AI2">
-        <v>0.08725008569759321</v>
+        <v>0.07655403273285152</v>
       </c>
       <c r="AJ2">
-        <v>-1.549421730135468</v>
+        <v>-1.236048801463377</v>
       </c>
       <c r="AK2">
-        <v>-1.445282608010403</v>
+        <v>-0.7384925605033735</v>
       </c>
       <c r="AL2">
-        <v>4.116</v>
+        <v>2.454</v>
       </c>
       <c r="AM2">
-        <v>4.116</v>
+        <v>2.454</v>
       </c>
       <c r="AN2">
-        <v>0.9230695627212707</v>
+        <v>0.6290141706595984</v>
       </c>
       <c r="AO2">
-        <v>8.894557823129253</v>
+        <v>14.11083944580277</v>
       </c>
       <c r="AP2">
-        <v>-5.725136319960534</v>
+        <v>-3.342534013582016</v>
       </c>
       <c r="AQ2">
-        <v>8.894557823129253</v>
+        <v>14.11083944580277</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0476</v>
+        <v>0.008539999999999999</v>
       </c>
       <c r="E3">
-        <v>0.0261</v>
+        <v>-0.083</v>
       </c>
       <c r="G3">
-        <v>0.09020458772473651</v>
+        <v>0.07702702702702703</v>
       </c>
       <c r="H3">
-        <v>0.09020458772473651</v>
+        <v>0.07702702702702703</v>
       </c>
       <c r="I3">
-        <v>0.05703657780533167</v>
+        <v>0.06936936936936937</v>
       </c>
       <c r="J3">
-        <v>0.04047652595389731</v>
+        <v>0.04227341435395126</v>
       </c>
       <c r="K3">
-        <v>12.5</v>
+        <v>9.06</v>
       </c>
       <c r="L3">
-        <v>0.03874767513949163</v>
+        <v>0.04081081081081081</v>
       </c>
       <c r="M3">
-        <v>7.68</v>
+        <v>3.75</v>
       </c>
       <c r="N3">
-        <v>0.07184284377923292</v>
+        <v>0.06996268656716417</v>
       </c>
       <c r="O3">
-        <v>0.6143999999999999</v>
+        <v>0.4139072847682119</v>
       </c>
       <c r="P3">
-        <v>7.68</v>
+        <v>3.75</v>
       </c>
       <c r="Q3">
-        <v>0.07184284377923292</v>
+        <v>0.06996268656716417</v>
       </c>
       <c r="R3">
-        <v>0.6143999999999999</v>
+        <v>0.4139072847682119</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>115.1</v>
+        <v>45.4</v>
       </c>
       <c r="V3">
-        <v>1.076707202993452</v>
+        <v>0.8470149253731343</v>
       </c>
       <c r="W3">
-        <v>0.1738525730180807</v>
+        <v>0.123433242506812</v>
       </c>
       <c r="X3">
-        <v>0.1267297736688165</v>
+        <v>0.2063587697834805</v>
       </c>
       <c r="Y3">
-        <v>0.04712279934926419</v>
-      </c>
-      <c r="Z3">
-        <v>5.467796610169491</v>
-      </c>
-      <c r="AA3">
-        <v>0.2213174114021571</v>
+        <v>-0.08292552727666855</v>
       </c>
       <c r="AB3">
-        <v>0.1204245557637927</v>
-      </c>
-      <c r="AC3">
-        <v>0.1008928556383645</v>
+        <v>0.193314458352432</v>
       </c>
       <c r="AD3">
-        <v>11</v>
+        <v>8.09</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11</v>
+        <v>8.09</v>
       </c>
       <c r="AG3">
-        <v>-104.1</v>
+        <v>-37.31</v>
       </c>
       <c r="AH3">
-        <v>0.09329940627650551</v>
+        <v>0.1311395688118009</v>
       </c>
       <c r="AI3">
-        <v>0.1303317535545024</v>
+        <v>0.1211259170534511</v>
       </c>
       <c r="AJ3">
-        <v>-37.17857142857127</v>
+        <v>-2.29036218538981</v>
       </c>
       <c r="AK3">
-        <v>3.390879478827363</v>
+        <v>-1.744273024777934</v>
       </c>
       <c r="AL3">
-        <v>1.47</v>
+        <v>0.824</v>
       </c>
       <c r="AM3">
-        <v>1.47</v>
+        <v>0.824</v>
       </c>
       <c r="AN3">
-        <v>0.5339805825242718</v>
+        <v>0.4703488372093023</v>
       </c>
       <c r="AO3">
-        <v>12.51700680272109</v>
+        <v>18.68932038834951</v>
       </c>
       <c r="AP3">
-        <v>-5.053398058252426</v>
+        <v>-2.169186046511628</v>
       </c>
       <c r="AQ3">
-        <v>12.51700680272109</v>
+        <v>18.68932038834951</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IGI Holdings Limited (KASE:IGIHL)</t>
+          <t>EFU Life Assurance Limited (KASE:EFUL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,46 +847,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0221</v>
+        <v>0.121</v>
       </c>
       <c r="E4">
-        <v>0.0917</v>
+        <v>-0.0363</v>
       </c>
       <c r="G4">
-        <v>0.1223118279569892</v>
+        <v>0.06562054208273894</v>
       </c>
       <c r="H4">
-        <v>0.1223118279569892</v>
+        <v>0.06562054208273894</v>
       </c>
       <c r="I4">
-        <v>0.1168010752688172</v>
+        <v>0.05706134094151212</v>
       </c>
       <c r="J4">
-        <v>0.09451416739319964</v>
+        <v>0.0340010138998597</v>
       </c>
       <c r="K4">
-        <v>15.2</v>
+        <v>7.26</v>
       </c>
       <c r="L4">
-        <v>0.2043010752688172</v>
+        <v>0.03452211126961483</v>
       </c>
       <c r="M4">
-        <v>5.87</v>
+        <v>6.57</v>
       </c>
       <c r="N4">
-        <v>0.04726247987117552</v>
+        <v>0.07243660418963617</v>
       </c>
       <c r="O4">
-        <v>0.3861842105263158</v>
+        <v>0.9049586776859505</v>
       </c>
       <c r="P4">
-        <v>5.87</v>
+        <v>6.57</v>
       </c>
       <c r="Q4">
-        <v>0.04726247987117552</v>
+        <v>0.07243660418963617</v>
       </c>
       <c r="R4">
-        <v>0.3861842105263158</v>
+        <v>0.9049586776859505</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +895,58 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>106.3</v>
       </c>
       <c r="V4">
-        <v>0.0644122383252818</v>
+        <v>1.17199558985667</v>
       </c>
       <c r="W4">
-        <v>0.05331462644686075</v>
+        <v>0.2167164179104478</v>
       </c>
       <c r="X4">
-        <v>0.1328669108891574</v>
+        <v>0.1936237516964757</v>
       </c>
       <c r="Y4">
-        <v>-0.0795522844422967</v>
-      </c>
-      <c r="Z4">
-        <v>0.2447448929241094</v>
-      </c>
-      <c r="AA4">
-        <v>0.02313185977845999</v>
+        <v>0.02309266621397207</v>
       </c>
       <c r="AB4">
-        <v>0.1207921404362254</v>
-      </c>
-      <c r="AC4">
-        <v>-0.09766028065776541</v>
+        <v>0.1909005813095309</v>
       </c>
       <c r="AD4">
-        <v>23.1</v>
+        <v>2.94</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>23.1</v>
+        <v>2.94</v>
       </c>
       <c r="AG4">
-        <v>15.1</v>
+        <v>-103.36</v>
       </c>
       <c r="AH4">
-        <v>0.1568228105906314</v>
+        <v>0.03139683895771038</v>
       </c>
       <c r="AI4">
-        <v>0.07497565725413827</v>
+        <v>0.1026536312849162</v>
       </c>
       <c r="AJ4">
-        <v>0.1083991385498923</v>
+        <v>8.164296998420223</v>
       </c>
       <c r="AK4">
-        <v>0.05031656114628457</v>
+        <v>1.330929693535926</v>
       </c>
       <c r="AL4">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>2.441860465116279</v>
-      </c>
-      <c r="AO4">
-        <v>3.448412698412698</v>
+        <v>0.2177777777777778</v>
       </c>
       <c r="AP4">
-        <v>1.596194503171247</v>
-      </c>
-      <c r="AQ4">
-        <v>3.448412698412698</v>
+        <v>-7.656296296296296</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EFU Life Assurance Limited (KASE:EFUL)</t>
+          <t>Adamjee Life Assurance Company Limited (KASE:ALIFE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,115 +966,112 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0567</v>
+        <v>2.735</v>
       </c>
       <c r="E5">
-        <v>-0.00265</v>
+        <v>1.715</v>
       </c>
       <c r="G5">
-        <v>0.06344086021505375</v>
+        <v>0.008987052551408985</v>
       </c>
       <c r="H5">
-        <v>0.06344086021505375</v>
+        <v>0.008987052551408985</v>
       </c>
       <c r="I5">
-        <v>0.04516129032258064</v>
+        <v>0.008643214424655425</v>
       </c>
       <c r="J5">
-        <v>0.0322430607651913</v>
+        <v>0.006498905502508086</v>
       </c>
       <c r="K5">
-        <v>9.17</v>
+        <v>0.985</v>
       </c>
       <c r="L5">
-        <v>0.03286738351254481</v>
+        <v>0.007501904036557501</v>
       </c>
       <c r="M5">
-        <v>8.789999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.07361809045226129</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.9585605234460195</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>8.789999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.07361809045226129</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.9585605234460195</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>151.2</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.266331658291457</v>
-      </c>
-      <c r="W5">
-        <v>0.2681286549707602</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>0.1212822209182912</v>
-      </c>
-      <c r="Y5">
-        <v>0.1468464340524691</v>
+        <v>0.1944674584001066</v>
       </c>
       <c r="Z5">
-        <v>-2.829901612739629</v>
+        <v>151.6639609541738</v>
       </c>
       <c r="AA5">
-        <v>-0.0912446896590767</v>
+        <v>0.9856497503772516</v>
       </c>
       <c r="AB5">
-        <v>0.1195838589605399</v>
+        <v>0.1910775157781167</v>
       </c>
       <c r="AC5">
-        <v>-0.2108285486196166</v>
+        <v>0.7945722345991348</v>
       </c>
       <c r="AD5">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.8657297302137132</v>
       </c>
       <c r="AF5">
-        <v>3.48</v>
+        <v>0.8657297302137132</v>
       </c>
       <c r="AG5">
-        <v>-147.72</v>
+        <v>0.8657297302137132</v>
       </c>
       <c r="AH5">
-        <v>0.0283203125</v>
+        <v>0.038707868719535</v>
       </c>
       <c r="AI5">
-        <v>0.09410492157923203</v>
+        <v>1</v>
       </c>
       <c r="AJ5">
-        <v>5.216101694915255</v>
+        <v>0.038707868719535</v>
       </c>
       <c r="AK5">
-        <v>1.293293643845211</v>
+        <v>1</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="AN5">
-        <v>0.24</v>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>7.095588235294117</v>
       </c>
       <c r="AP5">
-        <v>-10.18758620689655</v>
+        <v>0.5684371176715124</v>
+      </c>
+      <c r="AQ5">
+        <v>7.095588235294117</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IGI Life Insurance Limited (KASE:IGIL)</t>
+          <t>IGI Holdings Limited (KASE:IGIHL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1118,115 +1091,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0193</v>
+        <v>0.0223</v>
+      </c>
+      <c r="E6">
+        <v>-0.0478</v>
       </c>
       <c r="G6">
-        <v>-0.01113636363636364</v>
+        <v>0.1433734939759036</v>
       </c>
       <c r="H6">
-        <v>-0.01113636363636364</v>
+        <v>0.1433734939759036</v>
       </c>
       <c r="I6">
-        <v>-0.03842975206611571</v>
+        <v>0.1438898450946643</v>
       </c>
       <c r="J6">
-        <v>-0.03842975206611571</v>
+        <v>0.1105133346345618</v>
       </c>
       <c r="K6">
-        <v>-1.39</v>
+        <v>14.9</v>
       </c>
       <c r="L6">
-        <v>-0.02871900826446281</v>
+        <v>0.2564543889845095</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>3.4</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.05676126878130217</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>0.2281879194630872</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.05676126878130217</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>0.2281879194630872</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>3.38</v>
+        <v>3.82</v>
       </c>
       <c r="V6">
-        <v>0.09184782608695653</v>
+        <v>0.06377295492487479</v>
       </c>
       <c r="W6">
-        <v>-0.1077519379844961</v>
+        <v>0.05261299435028249</v>
       </c>
       <c r="X6">
-        <v>0.1209539355144818</v>
+        <v>0.2138196346362025</v>
       </c>
       <c r="Y6">
-        <v>-0.2287058734989779</v>
+        <v>-0.16120664028592</v>
       </c>
       <c r="Z6">
-        <v>5.854602636990444</v>
+        <v>0.1947703654039558</v>
       </c>
       <c r="AA6">
-        <v>-0.22499092778517</v>
+        <v>0.02152472256878324</v>
       </c>
       <c r="AB6">
-        <v>0.119464094572445</v>
+        <v>0.1930364448227551</v>
       </c>
       <c r="AC6">
-        <v>-0.344455022357615</v>
+        <v>-0.1715117222539718</v>
       </c>
       <c r="AD6">
-        <v>0.909</v>
+        <v>13.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.909</v>
+        <v>13.2</v>
       </c>
       <c r="AG6">
-        <v>-2.471</v>
+        <v>9.379999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.02410565117080803</v>
+        <v>0.1805745554035568</v>
       </c>
       <c r="AI6">
-        <v>0.0750681311421257</v>
+        <v>0.05736636245110821</v>
       </c>
       <c r="AJ6">
-        <v>-0.07197995863555597</v>
+        <v>0.135392609699769</v>
       </c>
       <c r="AK6">
-        <v>-0.2830793905372895</v>
+        <v>0.04145306699664132</v>
       </c>
       <c r="AL6">
-        <v>0.126</v>
+        <v>1.39</v>
       </c>
       <c r="AM6">
-        <v>0.126</v>
+        <v>1.39</v>
       </c>
       <c r="AN6">
-        <v>-0.568125</v>
+        <v>1.481481481481481</v>
       </c>
       <c r="AO6">
-        <v>-14.76190476190476</v>
+        <v>6.014388489208633</v>
       </c>
       <c r="AP6">
-        <v>1.544375</v>
+        <v>1.052749719416386</v>
       </c>
       <c r="AQ6">
-        <v>-14.76190476190476</v>
+        <v>6.014388489208633</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Askari Life Assurance Company Limited (KASE:ALAC)</t>
+          <t>IGI Life Insurance Limited (KASE:IGIL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1246,25 +1225,25 @@
         </is>
       </c>
       <c r="D7">
-        <v>1.179</v>
+        <v>-0.00267</v>
       </c>
       <c r="G7">
-        <v>-0.427710843373494</v>
+        <v>-0.07386018237082068</v>
       </c>
       <c r="H7">
-        <v>-0.427710843373494</v>
+        <v>-0.07386018237082068</v>
       </c>
       <c r="I7">
-        <v>-0.3644217638776998</v>
+        <v>-0.01996960486322188</v>
       </c>
       <c r="J7">
-        <v>-0.3644217638776998</v>
+        <v>-0.01996960486322188</v>
       </c>
       <c r="K7">
-        <v>-1.22</v>
+        <v>-0.534</v>
       </c>
       <c r="L7">
-        <v>-0.3674698795180723</v>
+        <v>-0.01623100303951368</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1288,67 +1267,195 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.361</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="V7">
-        <v>0.05553846153846154</v>
+        <v>0.07918994413407821</v>
       </c>
       <c r="W7">
-        <v>-1.745350500715308</v>
+        <v>-0.04767857142857143</v>
       </c>
       <c r="X7">
-        <v>0.121611232127691</v>
+        <v>0.1964738060239944</v>
       </c>
       <c r="Y7">
-        <v>-1.866961732842999</v>
+        <v>-0.2441523774525658</v>
       </c>
       <c r="Z7">
-        <v>6.853821685742335</v>
+        <v>3.769045709703288</v>
       </c>
       <c r="AA7">
-        <v>-2.497681788021451</v>
+        <v>-0.07526635353419636</v>
       </c>
       <c r="AB7">
-        <v>0.1195807244224369</v>
+        <v>0.1913375641322957</v>
       </c>
       <c r="AC7">
-        <v>-2.617262512443888</v>
+        <v>-0.2666039176664921</v>
       </c>
       <c r="AD7">
-        <v>0.099</v>
+        <v>0.422</v>
       </c>
       <c r="AE7">
-        <v>0.1194012803698165</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.2184012803698165</v>
+        <v>0.422</v>
       </c>
       <c r="AG7">
-        <v>-0.1425987196301835</v>
+        <v>-0.145</v>
       </c>
       <c r="AH7">
-        <v>0.03250792431942894</v>
+        <v>0.0556581376945397</v>
       </c>
       <c r="AI7">
-        <v>0.106620359234684</v>
+        <v>0.05313523042054898</v>
       </c>
       <c r="AJ7">
-        <v>-0.02243034745509857</v>
+        <v>-0.02066999287241625</v>
       </c>
       <c r="AK7">
-        <v>-0.08450788872160336</v>
+        <v>-0.01966101694915254</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="AN7">
-        <v>-0.08564013840830451</v>
+        <v>-0.7902621722846441</v>
+      </c>
+      <c r="AO7">
+        <v>-6.317307692307693</v>
       </c>
       <c r="AP7">
-        <v>0.1233552937977366</v>
+        <v>0.2715355805243445</v>
+      </c>
+      <c r="AQ7">
+        <v>-6.317307692307693</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Askari Life Assurance Company Limited (KASE:ALAC)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.862</v>
+      </c>
+      <c r="G8">
+        <v>-0.2990867579908676</v>
+      </c>
+      <c r="H8">
+        <v>-0.2990867579908676</v>
+      </c>
+      <c r="I8">
+        <v>-0.3248221786704242</v>
+      </c>
+      <c r="J8">
+        <v>-0.3248221786704242</v>
+      </c>
+      <c r="K8">
+        <v>-1.45</v>
+      </c>
+      <c r="L8">
+        <v>-0.3310502283105023</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0.655</v>
+      </c>
+      <c r="V8">
+        <v>0.1492027334851936</v>
+      </c>
+      <c r="W8">
+        <v>-0.7923497267759563</v>
+      </c>
+      <c r="X8">
+        <v>0.1920157867663939</v>
+      </c>
+      <c r="Y8">
+        <v>-0.9843655135423501</v>
+      </c>
+      <c r="Z8">
+        <v>2.709380503295872</v>
+      </c>
+      <c r="AA8">
+        <v>-0.8800668779277357</v>
+      </c>
+      <c r="AB8">
+        <v>0.1905095388855623</v>
+      </c>
+      <c r="AC8">
+        <v>-1.070576416813298</v>
+      </c>
+      <c r="AD8">
+        <v>0.028</v>
+      </c>
+      <c r="AE8">
+        <v>0.04860571288228913</v>
+      </c>
+      <c r="AF8">
+        <v>0.07660571288228912</v>
+      </c>
+      <c r="AG8">
+        <v>-0.5783942871177109</v>
+      </c>
+      <c r="AH8">
+        <v>0.01715076678054389</v>
+      </c>
+      <c r="AI8">
+        <v>-10.36012149146903</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.151745571469494</v>
+      </c>
+      <c r="AK8">
+        <v>0.8731873120984923</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>-0.02054292002934703</v>
+      </c>
+      <c r="AP8">
+        <v>0.4243538423460828</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07164999999999999</v>
+        <v>0.108</v>
       </c>
       <c r="E2">
-        <v>-0.04205</v>
+        <v>0.0579</v>
       </c>
       <c r="G2">
-        <v>0.05564660535979848</v>
+        <v>0.06971490470658419</v>
       </c>
       <c r="H2">
-        <v>0.05564660535979848</v>
+        <v>0.06971490470658419</v>
       </c>
       <c r="I2">
-        <v>0.05283185060454156</v>
+        <v>0.05666001747616631</v>
       </c>
       <c r="J2">
-        <v>0.04160696119089036</v>
+        <v>0.03945789743757021</v>
       </c>
       <c r="K2">
-        <v>30.221</v>
+        <v>27.176</v>
       </c>
       <c r="L2">
-        <v>0.04586026890042186</v>
+        <v>0.04266381990015385</v>
       </c>
       <c r="M2">
-        <v>13.72</v>
+        <v>10.909</v>
       </c>
       <c r="N2">
-        <v>0.05782929399367756</v>
+        <v>0.05194761904761905</v>
       </c>
       <c r="O2">
-        <v>0.4539889480824592</v>
+        <v>0.4014203709155137</v>
       </c>
       <c r="P2">
-        <v>13.72</v>
+        <v>10.909</v>
       </c>
       <c r="Q2">
-        <v>0.05782929399367756</v>
+        <v>0.05194761904761905</v>
       </c>
       <c r="R2">
-        <v>0.4539889480824592</v>
+        <v>0.4014203709155137</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>156.742</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="V2">
-        <v>0.6606617492096943</v>
+        <v>0.4702857142857143</v>
       </c>
       <c r="W2">
-        <v>0.08802311842854724</v>
+        <v>0.1612371882592789</v>
       </c>
       <c r="X2">
-        <v>0.1954706322120505</v>
+        <v>0.1943731777196703</v>
       </c>
       <c r="Y2">
-        <v>-0.1074475137835033</v>
+        <v>-0.03313598946039142</v>
       </c>
       <c r="Z2">
-        <v>2.129098112211642</v>
+        <v>2.509326557544959</v>
       </c>
       <c r="AA2">
-        <v>0.5035872364730174</v>
+        <v>0.197166998665317</v>
       </c>
       <c r="AB2">
-        <v>0.1912075399552062</v>
+        <v>0.1902065766591229</v>
       </c>
       <c r="AC2">
-        <v>0.3115302561725815</v>
+        <v>0.006828374456031142</v>
       </c>
       <c r="AD2">
-        <v>24.68</v>
+        <v>17.523</v>
       </c>
       <c r="AE2">
-        <v>0.9143354430960023</v>
+        <v>0.1635103401578819</v>
       </c>
       <c r="AF2">
-        <v>25.594335443096</v>
+        <v>17.68651034015788</v>
       </c>
       <c r="AG2">
-        <v>-131.147664556904</v>
+        <v>-81.07348965984212</v>
       </c>
       <c r="AH2">
-        <v>0.09737449886431736</v>
+        <v>0.07767921917611492</v>
       </c>
       <c r="AI2">
-        <v>0.07655403273285152</v>
+        <v>0.0563055737535257</v>
       </c>
       <c r="AJ2">
-        <v>-1.236048801463377</v>
+        <v>-0.6288349032789221</v>
       </c>
       <c r="AK2">
-        <v>-0.7384925605033735</v>
+        <v>-0.3764617541944086</v>
       </c>
       <c r="AL2">
-        <v>2.454</v>
+        <v>2.08</v>
       </c>
       <c r="AM2">
-        <v>2.454</v>
+        <v>2.08</v>
       </c>
       <c r="AN2">
-        <v>0.6290141706595984</v>
+        <v>0.4431938894228338</v>
       </c>
       <c r="AO2">
-        <v>14.11083944580277</v>
+        <v>17.3375</v>
       </c>
       <c r="AP2">
-        <v>-3.342534013582016</v>
+        <v>-2.050520756230516</v>
       </c>
       <c r="AQ2">
-        <v>14.11083944580277</v>
+        <v>17.3375</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jubilee Life Insurance Company Limited (KASE:JLICL)</t>
+          <t>Adamjee Life Assurance Company Limited (KASE:ALIFE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,47 +721,41 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.008539999999999999</v>
-      </c>
-      <c r="E3">
-        <v>-0.083</v>
-      </c>
       <c r="G3">
-        <v>0.07702702702702703</v>
+        <v>0.03350604490500864</v>
       </c>
       <c r="H3">
-        <v>0.07702702702702703</v>
+        <v>0.03350604490500864</v>
       </c>
       <c r="I3">
-        <v>0.06936936936936937</v>
+        <v>0.03773747841105354</v>
       </c>
       <c r="J3">
-        <v>0.04227341435395126</v>
+        <v>0.02411234944426179</v>
       </c>
       <c r="K3">
-        <v>9.06</v>
+        <v>2.92</v>
       </c>
       <c r="L3">
-        <v>0.04081081081081081</v>
+        <v>0.02521588946459413</v>
       </c>
       <c r="M3">
-        <v>3.75</v>
+        <v>0.869</v>
       </c>
       <c r="N3">
-        <v>0.06996268656716417</v>
+        <v>0.0365126050420168</v>
       </c>
       <c r="O3">
-        <v>0.4139072847682119</v>
+        <v>0.2976027397260274</v>
       </c>
       <c r="P3">
-        <v>3.75</v>
+        <v>0.869</v>
       </c>
       <c r="Q3">
-        <v>0.06996268656716417</v>
+        <v>0.0365126050420168</v>
       </c>
       <c r="R3">
-        <v>0.4139072847682119</v>
+        <v>0.2976027397260274</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,64 +764,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>45.4</v>
+        <v>28.8</v>
       </c>
       <c r="V3">
-        <v>0.8470149253731343</v>
-      </c>
-      <c r="W3">
-        <v>0.123433242506812</v>
+        <v>1.210084033613445</v>
       </c>
       <c r="X3">
-        <v>0.2063587697834805</v>
-      </c>
-      <c r="Y3">
-        <v>-0.08292552727666855</v>
+        <v>0.1903225047127052</v>
       </c>
       <c r="AB3">
-        <v>0.193314458352432</v>
+        <v>0.1890116850008007</v>
       </c>
       <c r="AD3">
-        <v>8.09</v>
+        <v>0.413</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.09</v>
+        <v>0.413</v>
       </c>
       <c r="AG3">
-        <v>-37.31</v>
+        <v>-28.387</v>
       </c>
       <c r="AH3">
-        <v>0.1311395688118009</v>
+        <v>0.01705695287655392</v>
       </c>
       <c r="AI3">
-        <v>0.1211259170534511</v>
+        <v>0.02750949177379604</v>
       </c>
       <c r="AJ3">
-        <v>-2.29036218538981</v>
+        <v>6.188576411597995</v>
       </c>
       <c r="AK3">
-        <v>-1.744273024777934</v>
+        <v>2.058968593602669</v>
       </c>
       <c r="AL3">
-        <v>0.824</v>
+        <v>0.049</v>
       </c>
       <c r="AM3">
-        <v>0.824</v>
+        <v>0.049</v>
       </c>
       <c r="AN3">
-        <v>0.4703488372093023</v>
+        <v>0.08978260869565217</v>
       </c>
       <c r="AO3">
-        <v>18.68932038834951</v>
+        <v>89.18367346938776</v>
       </c>
       <c r="AP3">
-        <v>-2.169186046511628</v>
+        <v>-6.17108695652174</v>
       </c>
       <c r="AQ3">
-        <v>18.68932038834951</v>
+        <v>89.18367346938776</v>
       </c>
     </row>
     <row r="4">
@@ -847,46 +835,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.121</v>
+        <v>0.137</v>
       </c>
       <c r="E4">
-        <v>-0.0363</v>
+        <v>0.0243</v>
       </c>
       <c r="G4">
-        <v>0.06562054208273894</v>
+        <v>0.07266074228959749</v>
       </c>
       <c r="H4">
-        <v>0.06562054208273894</v>
+        <v>0.07266074228959749</v>
       </c>
       <c r="I4">
-        <v>0.05706134094151212</v>
+        <v>0.05331939362258233</v>
       </c>
       <c r="J4">
-        <v>0.0340010138998597</v>
+        <v>0.03132514375326712</v>
       </c>
       <c r="K4">
-        <v>7.26</v>
+        <v>6.11</v>
       </c>
       <c r="L4">
-        <v>0.03452211126961483</v>
+        <v>0.03193936225823314</v>
       </c>
       <c r="M4">
-        <v>6.57</v>
+        <v>5.28</v>
       </c>
       <c r="N4">
-        <v>0.07243660418963617</v>
+        <v>0.0761904761904762</v>
       </c>
       <c r="O4">
-        <v>0.9049586776859505</v>
+        <v>0.8641571194762684</v>
       </c>
       <c r="P4">
-        <v>6.57</v>
+        <v>5.28</v>
       </c>
       <c r="Q4">
-        <v>0.07243660418963617</v>
+        <v>0.0761904761904762</v>
       </c>
       <c r="R4">
-        <v>0.9049586776859505</v>
+        <v>0.8641571194762684</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,46 +883,46 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>106.3</v>
+        <v>40</v>
       </c>
       <c r="V4">
-        <v>1.17199558985667</v>
+        <v>0.5772005772005773</v>
       </c>
       <c r="W4">
-        <v>0.2167164179104478</v>
+        <v>0.200327868852459</v>
       </c>
       <c r="X4">
-        <v>0.1936237516964757</v>
+        <v>0.1919594272835283</v>
       </c>
       <c r="Y4">
-        <v>0.02309266621397207</v>
+        <v>0.00836844156893074</v>
       </c>
       <c r="AB4">
-        <v>0.1909005813095309</v>
+        <v>0.1895301588774153</v>
       </c>
       <c r="AD4">
-        <v>2.94</v>
+        <v>2.27</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.94</v>
+        <v>2.27</v>
       </c>
       <c r="AG4">
-        <v>-103.36</v>
+        <v>-37.73</v>
       </c>
       <c r="AH4">
-        <v>0.03139683895771038</v>
+        <v>0.03171719994411067</v>
       </c>
       <c r="AI4">
-        <v>0.1026536312849162</v>
+        <v>0.1001323334803705</v>
       </c>
       <c r="AJ4">
-        <v>8.164296998420223</v>
+        <v>-1.195121951219512</v>
       </c>
       <c r="AK4">
-        <v>1.330929693535926</v>
+        <v>2.177149451817657</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -943,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.2177777777777778</v>
+        <v>0.1973913043478261</v>
       </c>
       <c r="AP4">
-        <v>-7.656296296296296</v>
+        <v>-3.280869565217391</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adamjee Life Assurance Company Limited (KASE:ALIFE)</t>
+          <t>Jubilee Life Insurance Company Limited (KASE:JLICL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,112 +954,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>2.735</v>
+        <v>0.053</v>
       </c>
       <c r="E5">
-        <v>1.715</v>
+        <v>-0.0579</v>
       </c>
       <c r="G5">
-        <v>0.008987052551408985</v>
+        <v>0.07079270877490462</v>
       </c>
       <c r="H5">
-        <v>0.008987052551408985</v>
+        <v>0.07079270877490462</v>
       </c>
       <c r="I5">
-        <v>0.008643214424655425</v>
+        <v>0.05383637134378973</v>
       </c>
       <c r="J5">
-        <v>0.006498905502508086</v>
+        <v>0.03091249709417604</v>
       </c>
       <c r="K5">
-        <v>0.985</v>
+        <v>7.17</v>
       </c>
       <c r="L5">
-        <v>0.007501904036557501</v>
+        <v>0.03039423484527342</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>2.64</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.05546218487394958</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.3682008368200837</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>2.64</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05546218487394958</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.3682008368200837</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>0.273109243697479</v>
+      </c>
+      <c r="W5">
+        <v>0.1221465076660988</v>
       </c>
       <c r="X5">
-        <v>0.1944674584001066</v>
+        <v>0.1997529972729304</v>
+      </c>
+      <c r="Y5">
+        <v>-0.07760648960683164</v>
       </c>
       <c r="Z5">
-        <v>151.6639609541738</v>
+        <v>11.02851799906498</v>
       </c>
       <c r="AA5">
-        <v>0.9856497503772516</v>
+        <v>0.3409190305991644</v>
       </c>
       <c r="AB5">
-        <v>0.1910775157781167</v>
+        <v>0.1916590812060411</v>
       </c>
       <c r="AC5">
-        <v>0.7945722345991348</v>
+        <v>0.1492599493931233</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE5">
-        <v>0.8657297302137132</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.8657297302137132</v>
+        <v>5.05</v>
       </c>
       <c r="AG5">
-        <v>0.8657297302137132</v>
+        <v>-7.95</v>
       </c>
       <c r="AH5">
-        <v>0.038707868719535</v>
+        <v>0.09591642924976258</v>
       </c>
       <c r="AI5">
-        <v>1</v>
+        <v>0.09156844968268359</v>
       </c>
       <c r="AJ5">
-        <v>0.038707868719535</v>
+        <v>-0.2005044136191677</v>
       </c>
       <c r="AK5">
-        <v>1</v>
+        <v>-0.1886120996441281</v>
       </c>
       <c r="AL5">
-        <v>0.136</v>
+        <v>0.506</v>
       </c>
       <c r="AM5">
-        <v>0.136</v>
+        <v>0.506</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.3607142857142857</v>
       </c>
       <c r="AO5">
-        <v>7.095588235294117</v>
+        <v>25.09881422924901</v>
       </c>
       <c r="AP5">
-        <v>0.5684371176715124</v>
+        <v>-0.5678571428571428</v>
       </c>
       <c r="AQ5">
-        <v>7.095588235294117</v>
+        <v>25.09881422924901</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IGI Holdings Limited (KASE:IGIHL)</t>
+          <t>IGI Life Insurance Limited (KASE:IGIL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,121 +1088,118 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0223</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="E6">
-        <v>-0.0478</v>
+        <v>0.988</v>
       </c>
       <c r="G6">
-        <v>0.1433734939759036</v>
+        <v>0.01240625</v>
       </c>
       <c r="H6">
-        <v>0.1433734939759036</v>
+        <v>0.01240625</v>
       </c>
       <c r="I6">
-        <v>0.1438898450946643</v>
+        <v>0.0174375</v>
       </c>
       <c r="J6">
-        <v>0.1105133346345618</v>
+        <v>0.01231048061389338</v>
       </c>
       <c r="K6">
-        <v>14.9</v>
+        <v>0.437</v>
       </c>
       <c r="L6">
-        <v>0.2564543889845095</v>
+        <v>0.01365625</v>
       </c>
       <c r="M6">
-        <v>3.4</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.05676126878130217</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.2281879194630872</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>3.4</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.05676126878130217</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.2281879194630872</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>3.82</v>
+        <v>1.46</v>
       </c>
       <c r="V6">
-        <v>0.06377295492487479</v>
+        <v>0.1793611793611793</v>
       </c>
       <c r="W6">
-        <v>0.05261299435028249</v>
+        <v>0.05811170212765958</v>
       </c>
       <c r="X6">
-        <v>0.2138196346362025</v>
+        <v>0.1903453134132309</v>
       </c>
       <c r="Y6">
-        <v>-0.16120664028592</v>
+        <v>-0.1322336112855713</v>
       </c>
       <c r="Z6">
-        <v>0.1947703654039558</v>
+        <v>4.338983050847459</v>
       </c>
       <c r="AA6">
-        <v>0.02152472256878324</v>
+        <v>0.05341496673146957</v>
       </c>
       <c r="AB6">
-        <v>0.1930364448227551</v>
+        <v>0.1890181672125306</v>
       </c>
       <c r="AC6">
-        <v>-0.1715117222539718</v>
+        <v>-0.135603200481061</v>
       </c>
       <c r="AD6">
-        <v>13.2</v>
+        <v>0.143</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>13.2</v>
+        <v>0.143</v>
       </c>
       <c r="AG6">
-        <v>9.379999999999999</v>
+        <v>-1.317</v>
       </c>
       <c r="AH6">
-        <v>0.1805745554035568</v>
+        <v>0.01726427622841965</v>
       </c>
       <c r="AI6">
-        <v>0.05736636245110821</v>
+        <v>0.02162407379404204</v>
       </c>
       <c r="AJ6">
-        <v>0.135392609699769</v>
+        <v>-0.1930235966583614</v>
       </c>
       <c r="AK6">
-        <v>0.04145306699664132</v>
+        <v>-0.2555792742091985</v>
       </c>
       <c r="AL6">
-        <v>1.39</v>
+        <v>0.015</v>
       </c>
       <c r="AM6">
-        <v>1.39</v>
+        <v>0.015</v>
       </c>
       <c r="AN6">
-        <v>1.481481481481481</v>
+        <v>0.2295345104333868</v>
       </c>
       <c r="AO6">
-        <v>6.014388489208633</v>
+        <v>37.2</v>
       </c>
       <c r="AP6">
-        <v>1.052749719416386</v>
+        <v>-2.113964686998395</v>
       </c>
       <c r="AQ6">
-        <v>6.014388489208633</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IGI Life Insurance Limited (KASE:IGIL)</t>
+          <t>IGI Holdings Limited (KASE:IGIHL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1225,115 +1219,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.00267</v>
+        <v>0.108</v>
+      </c>
+      <c r="E7">
+        <v>0.0915</v>
       </c>
       <c r="G7">
-        <v>-0.07386018237082068</v>
+        <v>0.187719298245614</v>
       </c>
       <c r="H7">
-        <v>-0.07386018237082068</v>
+        <v>0.187719298245614</v>
       </c>
       <c r="I7">
-        <v>-0.01996960486322188</v>
+        <v>0.157719298245614</v>
       </c>
       <c r="J7">
-        <v>-0.01996960486322188</v>
+        <v>0.105950257997936</v>
       </c>
       <c r="K7">
-        <v>-0.534</v>
+        <v>11.3</v>
       </c>
       <c r="L7">
-        <v>-0.01623100303951368</v>
+        <v>0.1982456140350877</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>2.12</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.03674176776429809</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>0.1876106194690265</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.03674176776429809</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.1876106194690265</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>0.5669999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="V7">
-        <v>0.07918994413407821</v>
+        <v>0.2634315424610052</v>
       </c>
       <c r="W7">
-        <v>-0.04767857142857143</v>
+        <v>0.05238757533611498</v>
       </c>
       <c r="X7">
-        <v>0.1964738060239944</v>
+        <v>0.2060491161697653</v>
       </c>
       <c r="Y7">
-        <v>-0.2441523774525658</v>
+        <v>-0.1536615408336503</v>
       </c>
       <c r="Z7">
-        <v>3.769045709703288</v>
+        <v>0.2532432912742136</v>
       </c>
       <c r="AA7">
-        <v>-0.07526635353419636</v>
+        <v>0.02683119204674939</v>
       </c>
       <c r="AB7">
-        <v>0.1913375641322957</v>
+        <v>0.1929144211529022</v>
       </c>
       <c r="AC7">
-        <v>-0.2666039176664921</v>
+        <v>-0.1660832291061529</v>
       </c>
       <c r="AD7">
-        <v>0.422</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.422</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AG7">
-        <v>-0.145</v>
+        <v>-5.66</v>
       </c>
       <c r="AH7">
-        <v>0.0556581376945397</v>
+        <v>0.1418798334324806</v>
       </c>
       <c r="AI7">
-        <v>0.05313523042054898</v>
+        <v>0.04478032294404807</v>
       </c>
       <c r="AJ7">
-        <v>-0.02066999287241625</v>
+        <v>-0.1087624903920061</v>
       </c>
       <c r="AK7">
-        <v>-0.01966101694915254</v>
+        <v>-0.02860897695107157</v>
       </c>
       <c r="AL7">
-        <v>0.104</v>
+        <v>1.51</v>
       </c>
       <c r="AM7">
-        <v>0.104</v>
+        <v>1.51</v>
       </c>
       <c r="AN7">
-        <v>-0.7902621722846441</v>
+        <v>1.007391763463569</v>
       </c>
       <c r="AO7">
-        <v>-6.317307692307693</v>
+        <v>5.953642384105961</v>
       </c>
       <c r="AP7">
-        <v>0.2715355805243445</v>
+        <v>-0.5976768743400211</v>
       </c>
       <c r="AQ7">
-        <v>-6.317307692307693</v>
+        <v>5.953642384105961</v>
       </c>
     </row>
     <row r="8">
@@ -1353,25 +1353,25 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.862</v>
+        <v>1.098</v>
       </c>
       <c r="G8">
-        <v>-0.2990867579908676</v>
+        <v>-0.2349397590361446</v>
       </c>
       <c r="H8">
-        <v>-0.2990867579908676</v>
+        <v>-0.2349397590361446</v>
       </c>
       <c r="I8">
-        <v>-0.3248221786704242</v>
+        <v>-0.1459241100465013</v>
       </c>
       <c r="J8">
-        <v>-0.3248221786704242</v>
+        <v>-0.1459241100465013</v>
       </c>
       <c r="K8">
-        <v>-1.45</v>
+        <v>-0.761</v>
       </c>
       <c r="L8">
-        <v>-0.3310502283105023</v>
+        <v>-0.1528112449799197</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1395,55 +1395,46 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.655</v>
+        <v>0.3</v>
       </c>
       <c r="V8">
-        <v>0.1492027334851936</v>
+        <v>0.08670520231213873</v>
       </c>
       <c r="W8">
-        <v>-0.7923497267759563</v>
+        <v>9.059523809523808</v>
       </c>
       <c r="X8">
-        <v>0.1920157867663939</v>
+        <v>0.1967869281558124</v>
       </c>
       <c r="Y8">
-        <v>-0.9843655135423501</v>
-      </c>
-      <c r="Z8">
-        <v>2.709380503295872</v>
-      </c>
-      <c r="AA8">
-        <v>-0.8800668779277357</v>
+        <v>8.862736881367995</v>
       </c>
       <c r="AB8">
-        <v>0.1905095388855623</v>
-      </c>
-      <c r="AC8">
-        <v>-1.070576416813298</v>
+        <v>0.1908829944408305</v>
       </c>
       <c r="AD8">
-        <v>0.028</v>
+        <v>0.107</v>
       </c>
       <c r="AE8">
-        <v>0.04860571288228913</v>
+        <v>0.1635103401578819</v>
       </c>
       <c r="AF8">
-        <v>0.07660571288228912</v>
+        <v>0.2705103401578819</v>
       </c>
       <c r="AG8">
-        <v>-0.5783942871177109</v>
+        <v>-0.0294896598421181</v>
       </c>
       <c r="AH8">
-        <v>0.01715076678054389</v>
+        <v>0.0725129581456765</v>
       </c>
       <c r="AI8">
-        <v>-10.36012149146903</v>
+        <v>0.1659053202518718</v>
       </c>
       <c r="AJ8">
-        <v>-0.151745571469494</v>
+        <v>-0.008596289449097216</v>
       </c>
       <c r="AK8">
-        <v>0.8731873120984923</v>
+        <v>-0.02216417186101596</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1452,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>-0.02054292002934703</v>
+        <v>-0.1633587786259542</v>
       </c>
       <c r="AP8">
-        <v>0.4243538423460828</v>
+        <v>0.04502238143834824</v>
       </c>
     </row>
   </sheetData>
